--- a/review/review_it.xlsx
+++ b/review/review_it.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,13 +34,22 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -60,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -71,7 +80,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -439,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -552,57 +564,71 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>• Rows marked 🌍 name the asker's nationality. Check that this sounds right.</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>• IMPORTANT: Mixing in German words (Ausbildung, Anmeldung) is fine if people really do that. But if there is an expression in your language, use it preferably.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>• Everyday wording is better than formal or legal wording.</t>
+          <t>• Rows marked 🌍 name the asker's nationality. Check that this sounds right.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>• Everyday wording is better than formal or legal wording.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>• Some questions use the masculine form (for example "Sono stato in Germania", "sono siriano"). If a neutral or feminine form would be more natural, say so in Comment.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-    </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Please don't change the topic of a question or the numbers in it (for example 48,000 euros, 32 years old).</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>When you are done, send this file back. Thank you!</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-    </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Queste frasi sono una prima bozza scritta da un modello di intelligenza artificiale (Claude Opus 5.5): possono contenere errori o suonare poco naturali, quindi correggile liberamente, come le scriveresti tu.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Riassunto: nel foglio Questions leggi la frase in inglese e la traduzione italiana. Se è corretta e suona naturale, scegli ✓ nella colonna OK? e non scrivere altro. Se c'è un errore o non suona naturale, scrivi la tua versione nella colonna Correction. Non cambiare il significato, correggi solo la lingua. Grazie!</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Importante: puoi usare parole tedesche (per esempio Ausbildung o Anmeldung) se le persone le usano davvero, ma se esiste un'espressione in italiano, è meglio usarla.</t>
         </is>
       </c>
     </row>
@@ -630,37 +656,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Italian</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>OK?</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -2073,27 +2099,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Term in the questions</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>German original (for you)</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>OK?</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
